--- a/AC6761_Artificial_Intelligence_Accounting/assignment/practice/work/case4-relational/Case4-关系表与核对.xlsx
+++ b/AC6761_Artificial_Intelligence_Accounting/assignment/practice/work/case4-relational/Case4-关系表与核对.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="答题总览" sheetId="1" r:id="R0e9680c3be69430d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="多重性" sheetId="2" r:id="R3a5a343ff8284673"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3原表与拆分" sheetId="3" r:id="R1c8af592674b4554"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4关系表" sheetId="4" r:id="R864fe0e210b6416f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核对与边界" sheetId="5" r:id="R676a9c1b98ce4279"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="答题总览" sheetId="1" r:id="R92f30b9c6f4a42fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="多重性" sheetId="2" r:id="Rd0a16dea390d464c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3原表与拆分" sheetId="3" r:id="R68adc8b3868748cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4关系表" sheetId="4" r:id="R1bce25fb731b4fac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核对与边界" sheetId="5" r:id="Rf757034c7f1743c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -365,7 +365,7 @@
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="15" t="str">
-        <x:v>两页照片逐项转录；官方解答及计分/提交要求待 Canvas 核实。编号按文本保留。</x:v>
+        <x:v>2026-10-26：本地官方 Word 与两照片逐项核对；计分/DDL/提交要求未实时核 Canvas。编号按文本保留。</x:v>
       </x:c>
       <x:c r="B3" s="15"/>
       <x:c r="C3" s="15"/>
@@ -402,7 +402,7 @@
         <x:v>Each purchase is made from exactly one supplier. A supplier may have zero or many purchases. The zero is on the Purchase end.</x:v>
       </x:c>
       <x:c r="D6" s="10" t="str">
-        <x:v>照片1 Q1；已发生采购</x:v>
+        <x:v>官解Q1端点已核；已发生采购</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="82" customHeight="1">
@@ -416,7 +416,7 @@
         <x:v>A purchase may have no return or several return events. Each return relates to one or more original purchases; combined returns allow multiple purchases.</x:v>
       </x:c>
       <x:c r="D7" s="10" t="str">
-        <x:v>照片1 Q2；分批/合并事件</x:v>
+        <x:v>官解Q2端点已核；批次与事件分清</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
@@ -430,7 +430,7 @@
         <x:v>Assuming CustomerID is the primary key, the Stephen row violates entity integrity. Assign a verified unique non-empty ID; do not invent one.</x:v>
       </x:c>
       <x:c r="D8" s="10" t="str">
-        <x:v>照片1表；ID为主键假设</x:v>
+        <x:v>官解：Violate entity integrity.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
@@ -438,13 +438,13 @@
         <x:v>3b</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>客户与销售分表；不合并两个 Andy</x:v>
+        <x:v>No：按当前四行不违反；拆表另属设计扩展</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
-        <x:v>Store customer attributes in Customer and reference CustomerID from Sale. Equal names and ages do not prove C123 and C124 identify the same person. The rows do not show a duplicate SaleID; referential integrity needs the customer master.</x:v>
+        <x:v>No. Matching names and ages under different CustomerID values do not establish repeated facts about the same customer. Separating customer details from sales is a separate design extension for repeated purchases.</x:v>
       </x:c>
       <x:c r="D9" s="10" t="str">
-        <x:v>照片2表；依赖/身份须分清</x:v>
+        <x:v>官解：No.；拆表为笔记设计扩展</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
@@ -458,7 +458,7 @@
         <x:v>Cashier(Cashier# PK, Name); CashReceipt(CashR# PK, Amount, Cashier# NOT NULL FK). Cashier# must not be unique in CashReceipt. Keep cashiers without receipts.</x:v>
       </x:c>
       <x:c r="D10" s="10" t="str">
-        <x:v>照片2 Q4；不建关联表</x:v>
+        <x:v>官解Q4四行外键已核</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26" customHeight="1">
@@ -2351,7 +2351,7 @@
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
       <x:c r="A18" s="17" t="str">
-        <x:v>来源状态：两页照片原题已逐项读取；Canvas Files 跳到 CityU 登录页。官方解答、计分、DDL和提交格式未取得；本工作簿是私有练习参考，保持 draft。</x:v>
+        <x:v>2026-10-26来源：两照片及Case 4 with Solution.docx已核；旧Canvas受阻是10/7历史，本轮未实时核计分/DDL/提交格式。保持draft，不代表本人已学会/提交。</x:v>
       </x:c>
       <x:c r="B18" s="17"/>
       <x:c r="C18" s="17"/>
